--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496D5B42-0F7B-40FF-9007-781CB0B7AC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6365D12E-BBF2-4459-A295-13B8AAF2C99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -194,6 +194,18 @@
   </si>
   <si>
     <t>Neutral</t>
+  </si>
+  <si>
+    <t>Chandrabhan Singh</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -880,26 +892,34 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>53</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12604997</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>54</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>55</v>
+      </c>
       <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -1011,25 +1031,47 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B7" s="14">
+        <v>440</v>
+      </c>
+      <c r="C7" s="14">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>30</v>
+      </c>
+      <c r="F7" s="14">
+        <v>320</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>10</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>570</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6365D12E-BBF2-4459-A295-13B8AAF2C99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE7B46F-0078-4D0E-B815-B2E356D80CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
 </sst>
 </file>
@@ -1075,25 +1078,47 @@
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B8" s="14">
+        <v>430</v>
+      </c>
+      <c r="C8" s="14">
+        <v>25</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>30</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>20</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>865</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>575</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE7B46F-0078-4D0E-B815-B2E356D80CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B27E255-0701-48A1-9905-0E76788D753A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,24 @@
   </si>
   <si>
     <t>Medium</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Feeling tired</t>
+  </si>
+  <si>
+    <t>Feeling good</t>
+  </si>
+  <si>
+    <t>Feeling happy</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1093,9 @@
       <c r="M7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
@@ -1119,73 +1139,147 @@
       <c r="M8" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B9" s="14">
+        <v>444</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>60</v>
+      </c>
+      <c r="E9" s="14">
+        <v>10</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>20</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>564</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>876</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B10" s="14">
+        <v>470</v>
+      </c>
+      <c r="C10" s="14">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>20</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>20</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B11" s="14">
+        <v>490</v>
+      </c>
+      <c r="C11" s="14">
+        <v>50</v>
+      </c>
+      <c r="D11" s="14">
+        <v>20</v>
+      </c>
+      <c r="E11" s="14">
+        <v>15</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>20</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B27E255-0701-48A1-9905-0E76788D753A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA02CD4-E354-467E-AA91-BBB2EDEE58A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>Feeling happy</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1282,48 +1285,96 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B12" s="14">
+        <v>510</v>
+      </c>
+      <c r="C12" s="14">
+        <v>10</v>
+      </c>
+      <c r="D12" s="14">
+        <v>30</v>
+      </c>
+      <c r="E12" s="14">
+        <v>10</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>10</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="14">
+        <v>520</v>
+      </c>
+      <c r="C13" s="14">
+        <v>10</v>
+      </c>
+      <c r="D13" s="14">
+        <v>40</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>10</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA02CD4-E354-467E-AA91-BBB2EDEE58A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2152CDA9-3E54-4F90-831C-8EE865DAE144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>Nas</t>
+  </si>
+  <si>
+    <t>ss</t>
   </si>
 </sst>
 </file>
@@ -1377,26 +1383,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B14" s="14">
+        <v>510</v>
+      </c>
+      <c r="C14" s="14">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
+        <v>80</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>150</v>
+      </c>
+      <c r="G14" s="14">
+        <v>3</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
@@ -1428,7 +1458,9 @@
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
+      <c r="H16" s="14" t="s">
+        <v>66</v>
+      </c>
       <c r="I16" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2152CDA9-3E54-4F90-831C-8EE865DAE144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199E70A3-EE51-4934-8FFF-FBAE27354276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,10 +232,10 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Nas</t>
+    <t>Satisfied</t>
   </si>
   <si>
-    <t>ss</t>
+    <t>Na</t>
   </si>
 </sst>
 </file>
@@ -1425,98 +1425,192 @@
         <v>57</v>
       </c>
       <c r="N14" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>65</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="E15" s="14">
+        <v>20</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>25</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14" t="s">
+      <c r="A16" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>45</v>
+      </c>
+      <c r="E16" s="14">
+        <v>20</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>15</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I16" s="15" t="str">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B17" s="14">
+        <v>600</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>35</v>
+      </c>
+      <c r="E17" s="14">
+        <v>20</v>
+      </c>
+      <c r="F17" s="14">
+        <v>50</v>
+      </c>
+      <c r="G17" s="14">
+        <v>1</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>685</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="14">
+        <v>520</v>
+      </c>
+      <c r="C18" s="14">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>55</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>55</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199E70A3-EE51-4934-8FFF-FBAE27354276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E36015-2A2E-488C-9D52-C142B23C9A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1613,26 +1613,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B19" s="14">
+        <v>520</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>65</v>
+      </c>
+      <c r="E19" s="14">
+        <v>40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>25</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E36015-2A2E-488C-9D52-C142B23C9A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59497813-2218-4C96-8F1B-AADAC51D9926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1659,26 +1659,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B20" s="14">
+        <v>530</v>
+      </c>
+      <c r="C20" s="14">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>55</v>
+      </c>
+      <c r="E20" s="14">
+        <v>40</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>35</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59497813-2218-4C96-8F1B-AADAC51D9926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4229CC-BD10-4B46-AABA-13AAF666CDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>Na</t>
+  </si>
+  <si>
+    <t>Feeling better</t>
   </si>
 </sst>
 </file>
@@ -1698,55 +1701,103 @@
         <v>52</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B21" s="14">
+        <v>550</v>
+      </c>
+      <c r="C21" s="14">
+        <v>45</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>45</v>
+      </c>
+      <c r="F21" s="14">
+        <v>150</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3</v>
+      </c>
+      <c r="H21" s="14">
+        <v>35</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>525</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B22" s="14">
+        <v>565</v>
+      </c>
+      <c r="C22" s="14">
+        <v>35</v>
+      </c>
+      <c r="D22" s="14">
+        <v>80</v>
+      </c>
+      <c r="E22" s="14">
+        <v>55</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>45</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/12604997.xlsx
+++ b/12604997.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4229CC-BD10-4B46-AABA-13AAF666CDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B5E309-841A-4853-AAA2-FC7B4397039C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1800,26 +1800,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B23" s="14">
+        <v>575</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>85</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>55</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>585</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
